--- a/artfynd/A 27017-2025 artfynd.xlsx
+++ b/artfynd/A 27017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1960,6 +1960,1129 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128050326</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fisklösen, Fisklösen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>529008</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6715113</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Knärot i hyggeskant, precis utanför hänsynsytan.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128051043</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>529033</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6715117</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter på en större yta, cirka 3,5 meter x 0,5 meter, nästan i mitten på hänsynsytan. Motsvarar ett av tidigare inlagda fynd (2025-03-18). Uppskattat antal - kan ha varit 300-400 plantor.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128050816</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>529027</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6715116</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Stegat 11 meter till hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128051607</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>529024</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6715109</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128051421</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>529039</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6715128</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Här återfanns den enda blomställningen vi såg inom hänsynsytan (överblommad). Stegade 22 meter till närmsta hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128051233</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>529033</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6715114</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128051193</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>529032</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6715117</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Moelven markerat denna växtplats med snitsel.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128051293</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>529032</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6715115</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128049928</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>529018</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6715119</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Väldigt nära kanten till avverkningen, stegat 3 meter till kantsnitsel.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27017-2025 artfynd.xlsx
+++ b/artfynd/A 27017-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128050816</v>
+        <v>128051607</v>
       </c>
       <c r="B15" t="n">
         <v>98459</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2246,18 +2246,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529027</v>
+        <v>529024</v>
       </c>
       <c r="R15" t="n">
-        <v>6715116</v>
+        <v>6715109</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2299,12 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stegat 11 meter till hyggeskant.</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,7 +2306,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2332,7 +2324,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128051607</v>
+        <v>128050816</v>
       </c>
       <c r="B16" t="n">
         <v>98459</v>
@@ -2362,7 +2354,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2375,16 +2367,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529024</v>
+        <v>529027</v>
       </c>
       <c r="R16" t="n">
-        <v>6715109</v>
+        <v>6715116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2416,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2426,7 +2420,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stegat 11 meter till hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,6 +2434,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27017-2025 artfynd.xlsx
+++ b/artfynd/A 27017-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128051193</v>
+        <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2749,6 +2749,8 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2758,7 +2760,7 @@
         <v>529032</v>
       </c>
       <c r="R19" t="n">
-        <v>6715117</v>
+        <v>6715115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2790,7 +2792,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2800,12 +2802,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Moelven markerat denna växtplats med snitsel.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2814,6 +2811,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2832,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128051293</v>
+        <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2860,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2875,8 +2873,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2886,7 +2882,7 @@
         <v>529032</v>
       </c>
       <c r="R20" t="n">
-        <v>6715115</v>
+        <v>6715117</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2918,7 +2914,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2928,7 +2924,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Moelven markerat denna växtplats med snitsel.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,7 +2938,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27017-2025 artfynd.xlsx
+++ b/artfynd/A 27017-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
         <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2709,7 +2709,7 @@
         <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
         <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 27017-2025 artfynd.xlsx
+++ b/artfynd/A 27017-2025 artfynd.xlsx
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson, Göran Ehn, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 27017-2025 artfynd.xlsx
+++ b/artfynd/A 27017-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27017-2025 artfynd.xlsx
+++ b/artfynd/A 27017-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27017-2025 artfynd.xlsx
+++ b/artfynd/A 27017-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128051607</v>
+        <v>128050816</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2246,16 +2246,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529024</v>
+        <v>529027</v>
       </c>
       <c r="R15" t="n">
-        <v>6715109</v>
+        <v>6715116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,7 +2289,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2299,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Stegat 11 meter till hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,6 +2313,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2317,17 +2325,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128050816</v>
+        <v>128051607</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2362,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2367,18 +2375,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529027</v>
+        <v>529024</v>
       </c>
       <c r="R16" t="n">
-        <v>6715116</v>
+        <v>6715109</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2410,7 +2416,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2420,12 +2426,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Stegat 11 meter till hyggeskant.</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2434,7 +2435,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128051293</v>
+        <v>128051193</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2749,8 +2749,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2760,7 +2758,7 @@
         <v>529032</v>
       </c>
       <c r="R19" t="n">
-        <v>6715115</v>
+        <v>6715117</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2792,7 +2790,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2802,7 +2800,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Moelven markerat denna växtplats med snitsel.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2811,7 +2814,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2830,10 +2832,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128051193</v>
+        <v>128051293</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,7 +2862,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2873,6 +2875,8 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2882,7 +2886,7 @@
         <v>529032</v>
       </c>
       <c r="R20" t="n">
-        <v>6715117</v>
+        <v>6715115</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2914,7 +2918,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2924,12 +2928,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Moelven markerat denna växtplats med snitsel.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,6 +2937,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27017-2025 artfynd.xlsx
+++ b/artfynd/A 27017-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128050816</v>
+        <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2246,18 +2246,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529027</v>
+        <v>529024</v>
       </c>
       <c r="R15" t="n">
-        <v>6715116</v>
+        <v>6715109</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2299,12 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stegat 11 meter till hyggeskant.</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,7 +2306,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2325,17 +2317,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128051607</v>
+        <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2362,7 +2354,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2375,16 +2367,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529024</v>
+        <v>529027</v>
       </c>
       <c r="R16" t="n">
-        <v>6715109</v>
+        <v>6715116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2416,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2426,7 +2420,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stegat 11 meter till hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,6 +2434,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128051193</v>
+        <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2749,6 +2749,8 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2758,7 +2760,7 @@
         <v>529032</v>
       </c>
       <c r="R19" t="n">
-        <v>6715117</v>
+        <v>6715115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2790,7 +2792,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2800,12 +2802,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Moelven markerat denna växtplats med snitsel.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2814,6 +2811,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2832,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128051293</v>
+        <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2860,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2875,8 +2873,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2886,7 +2882,7 @@
         <v>529032</v>
       </c>
       <c r="R20" t="n">
-        <v>6715115</v>
+        <v>6715117</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2918,7 +2914,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2928,7 +2924,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Moelven markerat denna växtplats med snitsel.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,7 +2938,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27017-2025 artfynd.xlsx
+++ b/artfynd/A 27017-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
